--- a/lab_2/results.xlsx
+++ b/lab_2/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gluon\FIT3143\lab_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CCAA83-3E71-4E84-A67E-27E35CC8429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B01FC3-C826-47A2-950D-78355FABE2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{C490FF79-F70F-4A57-9B82-FF3004BE1F9E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C490FF79-F70F-4A57-9B82-FF3004BE1F9E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -531,13 +531,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF34DD20-D4B6-49EF-845C-C54DDF36551F}">
   <dimension ref="A1:N14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -556,7 +556,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1</v>
       </c>
@@ -591,7 +591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10000000</v>
       </c>
@@ -637,7 +637,7 @@
         <v>4.5897388300365911</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>20000000</v>
       </c>
@@ -683,7 +683,7 @@
         <v>4.4346299393955775</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>50000000</v>
       </c>
@@ -729,7 +729,7 @@
         <v>4.2706056603566767</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>100000000</v>
       </c>
@@ -775,12 +775,12 @@
         <v>4.2658682331741575</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,7 +799,7 @@
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>1</v>
       </c>
@@ -834,7 +834,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10000000</v>
       </c>
@@ -880,7 +880,7 @@
         <v>4.6529870937976572</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>20000000</v>
       </c>
@@ -925,7 +925,7 @@
         <v>4.2364656571717525</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>50000000</v>
       </c>
@@ -970,7 +970,7 @@
         <v>4.6133249435875321</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>100000000</v>
       </c>
@@ -1029,20 +1029,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A393FC0-8CFB-4133-847F-6E38B47443F8}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
     <col min="8" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1065,7 +1065,7 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>10000000</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>1.870763</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>3.6122889999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>5.3538149999999991</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>7.0953409999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1393,7 +1393,7 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>10000000</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>1.9882919999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>3.9648759999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>5.9414599999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1715,9 +1715,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813D67-7D38-4993-89AF-C190AC66B662}">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10000000</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>15000000</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>0.92143200000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>20000000</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>1.276546</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25000000</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>1.8573759999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>30000000</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>2.0481099999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>35000000</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>2.4900039999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>40000000</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>3.2734380000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>45000000</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>3.5392540000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>50000000</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>4.0390699999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>55000000</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>5.2685750000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>60000000</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>5.8413110000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>65000000</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>6.9780009999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>70000000</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>7.6925299999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>75000000</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>9.9153140000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>80000000</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>10.056317</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>85000000</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>9.9292269999999991</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>90000000</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>10.169242000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>95000000</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>11.034445</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>100000000</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>11.505064000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>105000000</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>12.093972000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>110000000</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>13.145618000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>115000000</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>13.595419</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>120000000</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>14.814423</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>125000000</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>15.462853000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>130000000</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>16.194811999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>135000000</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>17.148802</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>140000000</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>18.527553999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>145000000</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>18.911625000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>150000000</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>20.430164999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>155000000</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>23.074195</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>160000000</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>23.935818999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>165000000</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>25.402840000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>170000000</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>25.120168</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>175000000</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>26.246811000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>180000000</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>26.803812000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>185000000</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>27.753297</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>190000000</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>27.647017999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>195000000</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>28.780218999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>200000000</v>
       </c>
